--- a/Team-Data/2007-08/3-4-2007-08.xlsx
+++ b/Team-Data/2007-08/3-4-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,28 +728,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E2" t="n">
         <v>25</v>
       </c>
       <c r="F2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>0.424</v>
+        <v>0.431</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
       </c>
       <c r="I2" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="J2" t="n">
         <v>79.40000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L2" t="n">
         <v>4.1</v>
@@ -691,25 +758,25 @@
         <v>12.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.34</v>
+        <v>0.338</v>
       </c>
       <c r="O2" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="P2" t="n">
-        <v>27.6</v>
+        <v>27.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.777</v>
+        <v>0.776</v>
       </c>
       <c r="R2" t="n">
         <v>12.6</v>
       </c>
       <c r="S2" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T2" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U2" t="n">
         <v>21.3</v>
@@ -727,25 +794,25 @@
         <v>5.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2.5</v>
+        <v>-2.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
         <v>20</v>
       </c>
       <c r="AF2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG2" t="n">
         <v>20</v>
@@ -763,16 +830,16 @@
         <v>21</v>
       </c>
       <c r="AL2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AN2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP2" t="n">
         <v>7</v>
@@ -793,10 +860,10 @@
         <v>17</v>
       </c>
       <c r="AV2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX2" t="n">
         <v>3</v>
@@ -808,10 +875,10 @@
         <v>16</v>
       </c>
       <c r="BA2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BB2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,7 +1003,7 @@
         <v>22</v>
       </c>
       <c r="AI3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -969,7 +1036,7 @@
         <v>10</v>
       </c>
       <c r="AT3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU3" t="n">
         <v>10</v>
@@ -984,13 +1051,13 @@
         <v>21</v>
       </c>
       <c r="AY3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ3" t="n">
         <v>25</v>
       </c>
       <c r="BA3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
         <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>0.35</v>
+        <v>0.339</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
@@ -1043,31 +1110,31 @@
         <v>35.6</v>
       </c>
       <c r="J4" t="n">
-        <v>79.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="K4" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L4" t="n">
         <v>6.2</v>
       </c>
       <c r="M4" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0.359</v>
+        <v>0.357</v>
       </c>
       <c r="O4" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="P4" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.711</v>
+        <v>0.709</v>
       </c>
       <c r="R4" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S4" t="n">
         <v>29.4</v>
@@ -1076,13 +1143,13 @@
         <v>40.6</v>
       </c>
       <c r="U4" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V4" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W4" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X4" t="n">
         <v>4.9</v>
@@ -1091,19 +1158,19 @@
         <v>6</v>
       </c>
       <c r="Z4" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="AA4" t="n">
         <v>21.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>-5.2</v>
+        <v>-5.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
         <v>24</v>
@@ -1118,7 +1185,7 @@
         <v>2</v>
       </c>
       <c r="AI4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ4" t="n">
         <v>20</v>
@@ -1133,7 +1200,7 @@
         <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO4" t="n">
         <v>17</v>
@@ -1154,19 +1221,19 @@
         <v>25</v>
       </c>
       <c r="AU4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AV4" t="n">
         <v>17</v>
       </c>
       <c r="AW4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX4" t="n">
         <v>14</v>
       </c>
-      <c r="AX4" t="n">
-        <v>13</v>
-      </c>
       <c r="AY4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ4" t="n">
         <v>23</v>
@@ -1175,10 +1242,10 @@
         <v>16</v>
       </c>
       <c r="BB4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -1207,34 +1274,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F5" t="n">
         <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J5" t="n">
         <v>84.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0.429</v>
+        <v>0.427</v>
       </c>
       <c r="L5" t="n">
         <v>5.5</v>
       </c>
       <c r="M5" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="N5" t="n">
         <v>0.349</v>
@@ -1243,7 +1310,7 @@
         <v>18.2</v>
       </c>
       <c r="P5" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="Q5" t="n">
         <v>0.743</v>
@@ -1252,13 +1319,13 @@
         <v>13.4</v>
       </c>
       <c r="S5" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T5" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U5" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="V5" t="n">
         <v>14.8</v>
@@ -1267,10 +1334,10 @@
         <v>7.6</v>
       </c>
       <c r="X5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z5" t="n">
         <v>21.4</v>
@@ -1279,28 +1346,28 @@
         <v>21.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>95.90000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.6</v>
+        <v>-2.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF5" t="n">
         <v>21</v>
       </c>
       <c r="AG5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ5" t="n">
         <v>5</v>
@@ -1318,7 +1385,7 @@
         <v>17</v>
       </c>
       <c r="AO5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP5" t="n">
         <v>20</v>
@@ -1336,16 +1403,16 @@
         <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV5" t="n">
         <v>16</v>
       </c>
       <c r="AW5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY5" t="n">
         <v>28</v>
@@ -1357,7 +1424,7 @@
         <v>14</v>
       </c>
       <c r="BB5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-0.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1479,7 +1546,7 @@
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI6" t="n">
         <v>19</v>
@@ -1488,7 +1555,7 @@
         <v>11</v>
       </c>
       <c r="AK6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL6" t="n">
         <v>12</v>
@@ -1500,7 +1567,7 @@
         <v>12</v>
       </c>
       <c r="AO6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP6" t="n">
         <v>15</v>
@@ -1536,7 +1603,7 @@
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB6" t="n">
         <v>16</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>3.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF7" t="n">
         <v>8</v>
@@ -1661,10 +1728,10 @@
         <v>8</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ7" t="n">
         <v>23</v>
@@ -1694,7 +1761,7 @@
         <v>19</v>
       </c>
       <c r="AS7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT7" t="n">
         <v>8</v>
@@ -1724,7 +1791,7 @@
         <v>12</v>
       </c>
       <c r="BC7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AE8" t="n">
         <v>12</v>
@@ -1852,7 +1919,7 @@
         <v>3</v>
       </c>
       <c r="AK8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL8" t="n">
         <v>15</v>
@@ -1882,10 +1949,10 @@
         <v>2</v>
       </c>
       <c r="AU8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1900,13 +1967,13 @@
         <v>13</v>
       </c>
       <c r="BA8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB8" t="n">
         <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -1935,49 +2002,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F9" t="n">
         <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>0.733</v>
+        <v>0.729</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
       </c>
       <c r="I9" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J9" t="n">
         <v>80</v>
       </c>
       <c r="K9" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L9" t="n">
         <v>6.1</v>
       </c>
       <c r="M9" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.376</v>
+        <v>0.374</v>
       </c>
       <c r="O9" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="P9" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.763</v>
+        <v>0.761</v>
       </c>
       <c r="R9" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S9" t="n">
         <v>29.6</v>
@@ -1995,7 +2062,7 @@
         <v>7.4</v>
       </c>
       <c r="X9" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y9" t="n">
         <v>3.8</v>
@@ -2004,16 +2071,16 @@
         <v>20.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>98.40000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2028,13 +2095,13 @@
         <v>29</v>
       </c>
       <c r="AI9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AJ9" t="n">
         <v>19</v>
       </c>
       <c r="AK9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL9" t="n">
         <v>18</v>
@@ -2043,22 +2110,22 @@
         <v>21</v>
       </c>
       <c r="AN9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AO9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AP9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AQ9" t="n">
         <v>13</v>
       </c>
       <c r="AR9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT9" t="n">
         <v>20</v>
@@ -2070,19 +2137,19 @@
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX9" t="n">
         <v>5</v>
       </c>
       <c r="AY9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ9" t="n">
         <v>14</v>
       </c>
       <c r="BA9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB9" t="n">
         <v>14</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -2117,46 +2184,46 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F10" t="n">
         <v>22</v>
       </c>
       <c r="G10" t="n">
-        <v>0.627</v>
+        <v>0.621</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>41.1</v>
+        <v>40.9</v>
       </c>
       <c r="J10" t="n">
-        <v>89.2</v>
+        <v>89</v>
       </c>
       <c r="K10" t="n">
-        <v>0.461</v>
+        <v>0.459</v>
       </c>
       <c r="L10" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="M10" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0.353</v>
+        <v>0.349</v>
       </c>
       <c r="O10" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="P10" t="n">
-        <v>25</v>
+        <v>25.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.749</v>
+        <v>0.748</v>
       </c>
       <c r="R10" t="n">
         <v>12.2</v>
@@ -2165,13 +2232,13 @@
         <v>29.9</v>
       </c>
       <c r="T10" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U10" t="n">
         <v>23.1</v>
       </c>
       <c r="V10" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W10" t="n">
         <v>9.1</v>
@@ -2180,22 +2247,22 @@
         <v>4.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z10" t="n">
         <v>23.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="AB10" t="n">
-        <v>110.6</v>
+        <v>110.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
@@ -2210,13 +2277,13 @@
         <v>17</v>
       </c>
       <c r="AI10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ10" t="n">
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AL10" t="n">
         <v>1</v>
@@ -2228,7 +2295,7 @@
         <v>16</v>
       </c>
       <c r="AO10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AP10" t="n">
         <v>14</v>
@@ -2246,10 +2313,10 @@
         <v>13</v>
       </c>
       <c r="AU10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW10" t="n">
         <v>2</v>
@@ -2264,13 +2331,13 @@
         <v>27</v>
       </c>
       <c r="BA10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BB10" t="n">
         <v>1</v>
       </c>
       <c r="BC10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -2377,25 +2444,25 @@
         <v>4.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AE11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF11" t="n">
         <v>6</v>
       </c>
       <c r="AG11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK11" t="n">
         <v>17</v>
@@ -2422,7 +2489,7 @@
         <v>11</v>
       </c>
       <c r="AS11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT11" t="n">
         <v>3</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
         <v>21</v>
@@ -2571,7 +2638,7 @@
         <v>21</v>
       </c>
       <c r="AH12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
         <v>9</v>
@@ -2595,7 +2662,7 @@
         <v>12</v>
       </c>
       <c r="AP12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ12" t="n">
         <v>9</v>
@@ -2616,7 +2683,7 @@
         <v>27</v>
       </c>
       <c r="AW12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-5.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2762,7 +2829,7 @@
         <v>25</v>
       </c>
       <c r="AK13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL13" t="n">
         <v>27</v>
@@ -2792,7 +2859,7 @@
         <v>29</v>
       </c>
       <c r="AU13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV13" t="n">
         <v>11</v>
@@ -2816,7 +2883,7 @@
         <v>29</v>
       </c>
       <c r="BC13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F14" t="n">
         <v>18</v>
       </c>
       <c r="G14" t="n">
-        <v>0.705</v>
+        <v>0.7</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
@@ -2863,7 +2930,7 @@
         <v>39.4</v>
       </c>
       <c r="J14" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>0.478</v>
@@ -2875,16 +2942,16 @@
         <v>20.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.367</v>
+        <v>0.368</v>
       </c>
       <c r="O14" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="P14" t="n">
-        <v>28.6</v>
+        <v>28.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.761</v>
+        <v>0.76</v>
       </c>
       <c r="R14" t="n">
         <v>10.7</v>
@@ -2905,7 +2972,7 @@
         <v>8.1</v>
       </c>
       <c r="X14" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y14" t="n">
         <v>4.7</v>
@@ -2914,16 +2981,16 @@
         <v>20.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>108</v>
+        <v>107.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2950,7 +3017,7 @@
         <v>10</v>
       </c>
       <c r="AM14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN14" t="n">
         <v>10</v>
@@ -2974,7 +3041,7 @@
         <v>4</v>
       </c>
       <c r="AU14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV14" t="n">
         <v>15</v>
@@ -2983,13 +3050,13 @@
         <v>6</v>
       </c>
       <c r="AX14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY14" t="n">
         <v>14</v>
       </c>
       <c r="AZ14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA14" t="n">
         <v>6</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -3027,28 +3094,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
       </c>
       <c r="F15" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G15" t="n">
-        <v>0.233</v>
+        <v>0.237</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J15" t="n">
-        <v>81.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L15" t="n">
         <v>7.7</v>
@@ -3057,22 +3124,22 @@
         <v>21.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.357</v>
+        <v>0.36</v>
       </c>
       <c r="O15" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="P15" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.734</v>
+        <v>0.733</v>
       </c>
       <c r="R15" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S15" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="T15" t="n">
         <v>41.3</v>
@@ -3087,10 +3154,10 @@
         <v>6.2</v>
       </c>
       <c r="X15" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z15" t="n">
         <v>19.5</v>
@@ -3102,10 +3169,10 @@
         <v>99.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.3</v>
+        <v>-6.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE15" t="n">
         <v>28</v>
@@ -3123,7 +3190,7 @@
         <v>12</v>
       </c>
       <c r="AJ15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK15" t="n">
         <v>16</v>
@@ -3135,13 +3202,13 @@
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AQ15" t="n">
         <v>21</v>
@@ -3150,13 +3217,13 @@
         <v>23</v>
       </c>
       <c r="AS15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT15" t="n">
         <v>19</v>
       </c>
       <c r="AU15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV15" t="n">
         <v>28</v>
@@ -3165,10 +3232,10 @@
         <v>27</v>
       </c>
       <c r="AX15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ15" t="n">
         <v>5</v>
@@ -3180,7 +3247,7 @@
         <v>13</v>
       </c>
       <c r="BC15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -3287,13 +3354,13 @@
         <v>-7.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
       </c>
       <c r="AF16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG16" t="n">
         <v>30</v>
@@ -3320,7 +3387,7 @@
         <v>20</v>
       </c>
       <c r="AO16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP16" t="n">
         <v>17</v>
@@ -3353,7 +3420,7 @@
         <v>4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA16" t="n">
         <v>15</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-6.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE17" t="n">
         <v>23</v>
@@ -3481,7 +3548,7 @@
         <v>23</v>
       </c>
       <c r="AH17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AI17" t="n">
         <v>18</v>
@@ -3499,10 +3566,10 @@
         <v>22</v>
       </c>
       <c r="AN17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP17" t="n">
         <v>22</v>
@@ -3541,7 +3608,7 @@
         <v>19</v>
       </c>
       <c r="BB17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BC17" t="n">
         <v>27</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E18" t="n">
         <v>12</v>
       </c>
       <c r="F18" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G18" t="n">
-        <v>0.203</v>
+        <v>0.207</v>
       </c>
       <c r="H18" t="n">
         <v>48.1</v>
@@ -3594,37 +3661,37 @@
         <v>83.09999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L18" t="n">
         <v>5.4</v>
       </c>
       <c r="M18" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="N18" t="n">
-        <v>0.337</v>
+        <v>0.335</v>
       </c>
       <c r="O18" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="P18" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.721</v>
+        <v>0.722</v>
       </c>
       <c r="R18" t="n">
         <v>12.2</v>
       </c>
       <c r="S18" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T18" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U18" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="V18" t="n">
         <v>15.3</v>
@@ -3642,16 +3709,16 @@
         <v>23.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>93.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>-7.5</v>
+        <v>-7.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
@@ -3666,7 +3733,7 @@
         <v>28</v>
       </c>
       <c r="AI18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AJ18" t="n">
         <v>8</v>
@@ -3693,19 +3760,19 @@
         <v>27</v>
       </c>
       <c r="AR18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS18" t="n">
         <v>25</v>
       </c>
       <c r="AT18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW18" t="n">
         <v>9</v>
@@ -3714,7 +3781,7 @@
         <v>29</v>
       </c>
       <c r="AY18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ18" t="n">
         <v>28</v>
@@ -3726,7 +3793,7 @@
         <v>30</v>
       </c>
       <c r="BC18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -3755,28 +3822,28 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19" t="n">
         <v>26</v>
       </c>
       <c r="F19" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G19" t="n">
-        <v>0.433</v>
+        <v>0.441</v>
       </c>
       <c r="H19" t="n">
         <v>48.4</v>
       </c>
       <c r="I19" t="n">
-        <v>34</v>
+        <v>34.1</v>
       </c>
       <c r="J19" t="n">
         <v>78.09999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.436</v>
+        <v>0.437</v>
       </c>
       <c r="L19" t="n">
         <v>6</v>
@@ -3785,34 +3852,34 @@
         <v>17.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O19" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="P19" t="n">
-        <v>27.6</v>
+        <v>27.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.725</v>
+        <v>0.726</v>
       </c>
       <c r="R19" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S19" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="T19" t="n">
         <v>42.6</v>
       </c>
       <c r="U19" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="V19" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W19" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="X19" t="n">
         <v>4.7</v>
@@ -3821,31 +3888,31 @@
         <v>4.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>94</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-4.8</v>
+        <v>-4.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE19" t="n">
         <v>19</v>
       </c>
       <c r="AF19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG19" t="n">
         <v>19</v>
       </c>
       <c r="AH19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3854,7 +3921,7 @@
         <v>28</v>
       </c>
       <c r="AK19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL19" t="n">
         <v>19</v>
@@ -3875,10 +3942,10 @@
         <v>25</v>
       </c>
       <c r="AR19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AS19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT19" t="n">
         <v>9</v>
@@ -3887,10 +3954,10 @@
         <v>5</v>
       </c>
       <c r="AV19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX19" t="n">
         <v>17</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>5</v>
       </c>
       <c r="AD20" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AE20" t="n">
         <v>5</v>
@@ -4036,13 +4103,13 @@
         <v>7</v>
       </c>
       <c r="AK20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM20" t="n">
         <v>9</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>8</v>
       </c>
       <c r="AN20" t="n">
         <v>2</v>
@@ -4057,7 +4124,7 @@
         <v>8</v>
       </c>
       <c r="AR20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS20" t="n">
         <v>14</v>
@@ -4066,7 +4133,7 @@
         <v>11</v>
       </c>
       <c r="AU20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV20" t="n">
         <v>3</v>
@@ -4078,7 +4145,7 @@
         <v>28</v>
       </c>
       <c r="AY20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ20" t="n">
         <v>2</v>
@@ -4087,7 +4154,7 @@
         <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC20" t="n">
         <v>6</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-6.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4209,7 +4276,7 @@
         <v>26</v>
       </c>
       <c r="AH21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI21" t="n">
         <v>27</v>
@@ -4272,7 +4339,7 @@
         <v>26</v>
       </c>
       <c r="BC21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E22" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F22" t="n">
         <v>23</v>
       </c>
       <c r="G22" t="n">
-        <v>0.629</v>
+        <v>0.623</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
@@ -4319,7 +4386,7 @@
         <v>36.9</v>
       </c>
       <c r="J22" t="n">
-        <v>78.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K22" t="n">
         <v>0.471</v>
@@ -4331,22 +4398,22 @@
         <v>24.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0.375</v>
+        <v>0.376</v>
       </c>
       <c r="O22" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="P22" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="Q22" t="n">
         <v>0.726</v>
       </c>
       <c r="R22" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T22" t="n">
         <v>42.2</v>
@@ -4367,22 +4434,22 @@
         <v>4.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="AB22" t="n">
         <v>104.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AD22" t="n">
         <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AF22" t="n">
         <v>11</v>
@@ -4409,10 +4476,10 @@
         <v>2</v>
       </c>
       <c r="AN22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP22" t="n">
         <v>2</v>
@@ -4421,10 +4488,10 @@
         <v>24</v>
       </c>
       <c r="AR22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT22" t="n">
         <v>12</v>
@@ -4442,19 +4509,19 @@
         <v>24</v>
       </c>
       <c r="AY22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ22" t="n">
         <v>15</v>
       </c>
       <c r="BA22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB22" t="n">
         <v>6</v>
       </c>
       <c r="BC22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -4561,13 +4628,13 @@
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>17</v>
       </c>
       <c r="AF23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG23" t="n">
         <v>17</v>
@@ -4582,7 +4649,7 @@
         <v>16</v>
       </c>
       <c r="AK23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL23" t="n">
         <v>30</v>
@@ -4594,7 +4661,7 @@
         <v>30</v>
       </c>
       <c r="AO23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP23" t="n">
         <v>13</v>
@@ -4624,16 +4691,16 @@
         <v>11</v>
       </c>
       <c r="AY23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA23" t="n">
         <v>20</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BC23" t="n">
         <v>15</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -4665,46 +4732,46 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E24" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F24" t="n">
         <v>20</v>
       </c>
       <c r="G24" t="n">
-        <v>0.667</v>
+        <v>0.661</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="J24" t="n">
-        <v>83.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="K24" t="n">
-        <v>0.492</v>
+        <v>0.493</v>
       </c>
       <c r="L24" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="N24" t="n">
         <v>0.384</v>
       </c>
       <c r="O24" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="P24" t="n">
-        <v>23.3</v>
+        <v>22.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.792</v>
+        <v>0.791</v>
       </c>
       <c r="R24" t="n">
         <v>8.699999999999999</v>
@@ -4716,7 +4783,7 @@
         <v>40.9</v>
       </c>
       <c r="U24" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="V24" t="n">
         <v>14.1</v>
@@ -4725,28 +4792,28 @@
         <v>6.9</v>
       </c>
       <c r="X24" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="Y24" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Z24" t="n">
         <v>19.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>109.3</v>
+        <v>109.5</v>
       </c>
       <c r="AC24" t="n">
         <v>4.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF24" t="n">
         <v>6</v>
@@ -4758,7 +4825,7 @@
         <v>18</v>
       </c>
       <c r="AI24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ24" t="n">
         <v>6</v>
@@ -4776,7 +4843,7 @@
         <v>4</v>
       </c>
       <c r="AO24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP24" t="n">
         <v>24</v>
@@ -4791,7 +4858,7 @@
         <v>7</v>
       </c>
       <c r="AT24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
@@ -4809,7 +4876,7 @@
         <v>1</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA24" t="n">
         <v>21</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -4847,22 +4914,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E25" t="n">
         <v>31</v>
       </c>
       <c r="F25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G25" t="n">
-        <v>0.508</v>
+        <v>0.517</v>
       </c>
       <c r="H25" t="n">
         <v>48.7</v>
       </c>
       <c r="I25" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="J25" t="n">
         <v>79</v>
@@ -4871,13 +4938,13 @@
         <v>0.45</v>
       </c>
       <c r="L25" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="M25" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.372</v>
+        <v>0.375</v>
       </c>
       <c r="O25" t="n">
         <v>17.9</v>
@@ -4886,7 +4953,7 @@
         <v>23.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.766</v>
+        <v>0.764</v>
       </c>
       <c r="R25" t="n">
         <v>10.5</v>
@@ -4898,7 +4965,7 @@
         <v>40.3</v>
       </c>
       <c r="U25" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="V25" t="n">
         <v>13.2</v>
@@ -4913,19 +4980,19 @@
         <v>3.8</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AA25" t="n">
         <v>20.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>95.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.9</v>
+        <v>-0.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
         <v>15</v>
@@ -4940,7 +5007,7 @@
         <v>1</v>
       </c>
       <c r="AI25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ25" t="n">
         <v>24</v>
@@ -4955,10 +5022,10 @@
         <v>19</v>
       </c>
       <c r="AN25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO25" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP25" t="n">
         <v>23</v>
@@ -4967,13 +5034,13 @@
         <v>12</v>
       </c>
       <c r="AR25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS25" t="n">
         <v>21</v>
       </c>
       <c r="AT25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU25" t="n">
         <v>19</v>
@@ -4988,10 +5055,10 @@
         <v>20</v>
       </c>
       <c r="AY25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA25" t="n">
         <v>18</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -5029,46 +5096,46 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
         <v>27</v>
       </c>
       <c r="F26" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G26" t="n">
-        <v>0.45</v>
+        <v>0.458</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J26" t="n">
-        <v>79.8</v>
+        <v>79.5</v>
       </c>
       <c r="K26" t="n">
         <v>0.457</v>
       </c>
       <c r="L26" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M26" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.377</v>
+        <v>0.378</v>
       </c>
       <c r="O26" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="P26" t="n">
-        <v>27.7</v>
+        <v>27.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.79</v>
+        <v>0.789</v>
       </c>
       <c r="R26" t="n">
         <v>10.5</v>
@@ -5080,7 +5147,7 @@
         <v>40.3</v>
       </c>
       <c r="U26" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="V26" t="n">
         <v>16.1</v>
@@ -5089,25 +5156,25 @@
         <v>7.9</v>
       </c>
       <c r="X26" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y26" t="n">
         <v>5.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>101.3</v>
+        <v>101.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5122,7 +5189,7 @@
         <v>18</v>
       </c>
       <c r="AI26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ26" t="n">
         <v>21</v>
@@ -5149,13 +5216,13 @@
         <v>5</v>
       </c>
       <c r="AR26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS26" t="n">
         <v>22</v>
       </c>
       <c r="AT26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU26" t="n">
         <v>28</v>
@@ -5167,16 +5234,16 @@
         <v>8</v>
       </c>
       <c r="AX26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ26" t="n">
         <v>24</v>
       </c>
       <c r="BA26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB26" t="n">
         <v>8</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -5211,64 +5278,64 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E27" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F27" t="n">
         <v>17</v>
       </c>
       <c r="G27" t="n">
-        <v>0.712</v>
+        <v>0.707</v>
       </c>
       <c r="H27" t="n">
         <v>48.2</v>
       </c>
       <c r="I27" t="n">
-        <v>35.6</v>
+        <v>35.8</v>
       </c>
       <c r="J27" t="n">
         <v>78.3</v>
       </c>
       <c r="K27" t="n">
-        <v>0.455</v>
+        <v>0.457</v>
       </c>
       <c r="L27" t="n">
         <v>7.8</v>
       </c>
       <c r="M27" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="N27" t="n">
         <v>0.377</v>
       </c>
       <c r="O27" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="P27" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.759</v>
+        <v>0.758</v>
       </c>
       <c r="R27" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T27" t="n">
-        <v>41.7</v>
+        <v>41.5</v>
       </c>
       <c r="U27" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="V27" t="n">
         <v>12.8</v>
       </c>
       <c r="W27" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="X27" t="n">
         <v>4</v>
@@ -5277,19 +5344,19 @@
         <v>4.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>95.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE27" t="n">
         <v>4</v>
@@ -5301,7 +5368,7 @@
         <v>3</v>
       </c>
       <c r="AH27" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI27" t="n">
         <v>23</v>
@@ -5310,10 +5377,10 @@
         <v>27</v>
       </c>
       <c r="AK27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM27" t="n">
         <v>6</v>
@@ -5328,19 +5395,19 @@
         <v>27</v>
       </c>
       <c r="AQ27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR27" t="n">
         <v>24</v>
       </c>
       <c r="AS27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU27" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AV27" t="n">
         <v>4</v>
@@ -5358,10 +5425,10 @@
         <v>1</v>
       </c>
       <c r="BA27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC27" t="n">
         <v>5</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E28" t="n">
         <v>16</v>
       </c>
       <c r="F28" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G28" t="n">
-        <v>0.267</v>
+        <v>0.271</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
@@ -5414,7 +5481,7 @@
         <v>85.3</v>
       </c>
       <c r="K28" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L28" t="n">
         <v>4.1</v>
@@ -5423,10 +5490,10 @@
         <v>12.1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.34</v>
+        <v>0.341</v>
       </c>
       <c r="O28" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P28" t="n">
         <v>22.9</v>
@@ -5441,10 +5508,10 @@
         <v>33.4</v>
       </c>
       <c r="T28" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
       <c r="U28" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V28" t="n">
         <v>16.3</v>
@@ -5453,13 +5520,13 @@
         <v>6.4</v>
       </c>
       <c r="X28" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AA28" t="n">
         <v>19.8</v>
@@ -5468,10 +5535,10 @@
         <v>97</v>
       </c>
       <c r="AC28" t="n">
-        <v>-7.2</v>
+        <v>-7.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE28" t="n">
         <v>27</v>
@@ -5492,19 +5559,19 @@
         <v>4</v>
       </c>
       <c r="AK28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AN28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP28" t="n">
         <v>25</v>
@@ -5513,7 +5580,7 @@
         <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS28" t="n">
         <v>2</v>
@@ -5522,7 +5589,7 @@
         <v>1</v>
       </c>
       <c r="AU28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV28" t="n">
         <v>30</v>
@@ -5531,13 +5598,13 @@
         <v>25</v>
       </c>
       <c r="AX28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AZ28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA28" t="n">
         <v>27</v>
@@ -5546,7 +5613,7 @@
         <v>17</v>
       </c>
       <c r="BC28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E29" t="n">
         <v>32</v>
       </c>
       <c r="F29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G29" t="n">
-        <v>0.542</v>
+        <v>0.552</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
@@ -5593,28 +5660,28 @@
         <v>37.8</v>
       </c>
       <c r="J29" t="n">
-        <v>81.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.466</v>
+        <v>0.467</v>
       </c>
       <c r="L29" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M29" t="n">
         <v>18.4</v>
       </c>
       <c r="N29" t="n">
-        <v>0.41</v>
+        <v>0.413</v>
       </c>
       <c r="O29" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="P29" t="n">
         <v>20.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="R29" t="n">
         <v>9.699999999999999</v>
@@ -5623,10 +5690,10 @@
         <v>30.7</v>
       </c>
       <c r="T29" t="n">
-        <v>40.5</v>
+        <v>40.3</v>
       </c>
       <c r="U29" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="V29" t="n">
         <v>11.7</v>
@@ -5635,31 +5702,31 @@
         <v>6.8</v>
       </c>
       <c r="X29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y29" t="n">
         <v>4</v>
       </c>
-      <c r="Y29" t="n">
-        <v>3.9</v>
-      </c>
       <c r="Z29" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>99.90000000000001</v>
+        <v>100.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE29" t="n">
         <v>14</v>
       </c>
       <c r="AF29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG29" t="n">
         <v>14</v>
@@ -5695,7 +5762,7 @@
         <v>2</v>
       </c>
       <c r="AR29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS29" t="n">
         <v>15</v>
@@ -5704,7 +5771,7 @@
         <v>26</v>
       </c>
       <c r="AU29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV29" t="n">
         <v>2</v>
@@ -5713,22 +5780,22 @@
         <v>21</v>
       </c>
       <c r="AX29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY29" t="n">
         <v>5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA29" t="n">
         <v>29</v>
       </c>
       <c r="BB29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -5835,10 +5902,10 @@
         <v>5.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF30" t="n">
         <v>8</v>
@@ -5874,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="AQ30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR30" t="n">
         <v>16</v>
@@ -5898,7 +5965,7 @@
         <v>23</v>
       </c>
       <c r="AY30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ30" t="n">
         <v>30</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
@@ -6017,19 +6084,19 @@
         <v>0.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
       </c>
       <c r="AF31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG31" t="n">
         <v>16</v>
       </c>
       <c r="AH31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI31" t="n">
         <v>20</v>
@@ -6047,7 +6114,7 @@
         <v>11</v>
       </c>
       <c r="AN31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO31" t="n">
         <v>11</v>
@@ -6062,7 +6129,7 @@
         <v>5</v>
       </c>
       <c r="AS31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT31" t="n">
         <v>14</v>
@@ -6071,13 +6138,13 @@
         <v>29</v>
       </c>
       <c r="AV31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW31" t="n">
         <v>7</v>
       </c>
       <c r="AX31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY31" t="n">
         <v>10</v>
@@ -6086,7 +6153,7 @@
         <v>3</v>
       </c>
       <c r="BA31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB31" t="n">
         <v>15</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-4-2007-08</t>
+          <t>2008-03-04</t>
         </is>
       </c>
     </row>
